--- a/enhancements/test-files/07_Dates_pc0404_2026.xlsx
+++ b/enhancements/test-files/07_Dates_pc0404_2026.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -432,6 +432,13 @@
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -480,6 +487,41 @@
           <t>Transaction Effective Date</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>MarketProvider</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Transaction Detail</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>GrossCommissionAmount</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>CommissionPct</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>ProducerCommissionAmount</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ProducerCommissionPct</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -492,12 +534,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Zenith Insurance Group</t>
+          <t>Heritage Casualty Co</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Metro Agency Group</t>
+          <t>Coastal Risk Advisors</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -506,7 +548,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>11291.13</v>
+        <v>1957.64</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -514,10 +556,35 @@
         </is>
       </c>
       <c r="H2" s="2" t="n">
-        <v>45726</v>
+        <v>45796</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>46019</v>
+        <v>46022</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Lloyd's</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Cancellation</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>234.92</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N2" t="n">
+        <v>119.81</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.0612</v>
+      </c>
+      <c r="P2" t="n">
+        <v>115.11</v>
       </c>
     </row>
     <row r="3">
@@ -531,12 +598,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Liberty Mutual</t>
+          <t>Global Assurance Corp</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Brown &amp; Brown</t>
+          <t>Metro Agency Group</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -545,7 +612,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2248.21</v>
+        <v>6020.93</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -553,10 +620,35 @@
         </is>
       </c>
       <c r="H3" s="2" t="n">
-        <v>45941</v>
+        <v>45793</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>46021</v>
+        <v>46025</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Lloyd's</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Endorsement</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>722.51</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N3" t="n">
+        <v>469.63</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="P3" t="n">
+        <v>252.88</v>
       </c>
     </row>
     <row r="4">
@@ -570,7 +662,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>National Indemnity Co</t>
+          <t>Global Assurance Corp</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -584,7 +676,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>18116.37</v>
+        <v>9657.379999999999</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -592,10 +684,35 @@
         </is>
       </c>
       <c r="H4" s="2" t="n">
-        <v>45882</v>
+        <v>45938</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>46027</v>
+        <v>46029</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Excess &amp; Surplus</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>New Business</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>1158.89</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N4" t="n">
+        <v>475.14</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.0492</v>
+      </c>
+      <c r="P4" t="n">
+        <v>683.75</v>
       </c>
     </row>
     <row r="5">
@@ -609,12 +726,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Liberty Mutual</t>
+          <t>Zenith Insurance Group</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Metro Agency Group</t>
+          <t>Coastal Risk Advisors</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -623,7 +740,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>24673.21</v>
+        <v>9580.040000000001</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -631,10 +748,35 @@
         </is>
       </c>
       <c r="H5" s="2" t="n">
-        <v>45869</v>
+        <v>45859</v>
       </c>
       <c r="I5" s="2" t="n">
         <v>46031</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Admitted</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Endorsement</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>1149.6</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N5" t="n">
+        <v>563.3</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.0588</v>
+      </c>
+      <c r="P5" t="n">
+        <v>586.3</v>
       </c>
     </row>
     <row r="6">
@@ -648,7 +790,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Zenith Insurance Group</t>
+          <t>National Indemnity Co</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -662,7 +804,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>24844.75</v>
+        <v>16742.8</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -670,10 +812,35 @@
         </is>
       </c>
       <c r="H6" s="2" t="n">
-        <v>46004</v>
+        <v>45887</v>
       </c>
       <c r="I6" s="2" t="n">
         <v>46031</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Specialty</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Cancellation</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>2009.14</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1004.57</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1004.57</v>
       </c>
     </row>
     <row r="7">
@@ -692,7 +859,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Brown &amp; Brown</t>
+          <t>Coastal Risk Advisors</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -701,7 +868,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1100.91</v>
+        <v>13937.23</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -709,10 +876,35 @@
         </is>
       </c>
       <c r="H7" s="2" t="n">
-        <v>45977</v>
+        <v>45784</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>46034</v>
+        <v>46035</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Admitted</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>New Business</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>1672.47</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N7" t="n">
+        <v>953.3099999999999</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.0684</v>
+      </c>
+      <c r="P7" t="n">
+        <v>719.16</v>
       </c>
     </row>
     <row r="8">
@@ -726,7 +918,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Global Assurance Corp</t>
+          <t>Zenith Insurance Group</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -740,7 +932,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>19646.45</v>
+        <v>19523.19</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -748,10 +940,35 @@
         </is>
       </c>
       <c r="H8" s="2" t="n">
-        <v>45870</v>
+        <v>45985</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>46036</v>
+        <v>46038</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Excess &amp; Surplus</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Renewal</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>2342.78</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1101.11</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.0564</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1241.67</v>
       </c>
     </row>
     <row r="9">
@@ -765,12 +982,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Zenith Insurance Group</t>
+          <t>Heritage Casualty Co</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Coastal Risk Advisors</t>
+          <t>Apex Insurance Brokers</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -779,16 +996,41 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>6496.86</v>
+        <v>19699.34</v>
       </c>
       <c r="G9" t="n">
         <v>46030</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>45923</v>
+        <v>45811</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>46043</v>
+        <v>46040</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Specialty</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>New Business</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>2363.92</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1181.96</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1181.96</v>
       </c>
     </row>
     <row r="10">
@@ -807,7 +1049,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Metro Agency Group</t>
+          <t>Coastal Risk Advisors</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -816,7 +1058,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>6650.44</v>
+        <v>5588.5</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -824,10 +1066,35 @@
         </is>
       </c>
       <c r="H10" s="2" t="n">
-        <v>45887</v>
+        <v>45858</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>46047</v>
+        <v>46044</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Admitted</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Renewal</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>670.62</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N10" t="n">
+        <v>362.13</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.0648</v>
+      </c>
+      <c r="P10" t="n">
+        <v>308.49</v>
       </c>
     </row>
     <row r="11">
@@ -841,12 +1108,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Global Assurance Corp</t>
+          <t>Heritage Casualty Co</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Apex Insurance Brokers</t>
+          <t>Metro Agency Group</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -855,7 +1122,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>24424.54</v>
+        <v>14139.65</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -863,10 +1130,35 @@
         </is>
       </c>
       <c r="H11" s="2" t="n">
-        <v>45753</v>
+        <v>45804</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>46023</v>
+        <v>46018</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Specialty</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Renewal</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>1696.76</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1051.99</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.07439999999999999</v>
+      </c>
+      <c r="P11" t="n">
+        <v>644.77</v>
       </c>
     </row>
   </sheetData>
